--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="49" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="49" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.33.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.33.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0033.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0033.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: with these words.â€”" A Defendant is to answer or demur,</t>
+          <t>L15: stray/suspicious non-ASCII glyph(s): U+6D77 CJK UNIFIED IDEOGRAPH-6D77 | isolated marker/symbol line :: 海</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Plaintiffâ€™s Solicitor.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]26 THE WRIT.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]26 THE WRIT.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L7: isolated marker/symbol line :: 185</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -676,19 +680,15 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN :: VÃ­bar</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: against you as the Court shall think just upon the plaintiffâ€™s</t>
-        </is>
-      </c>
+          <t>L16: stray/suspicious non-ASCII glyph(s): U+91D1 CJK UNIFIED IDEOGRAPH-91D1 | isolated marker/symbol line :: 金</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L16: isolated marker/symbol line :: é‡‘</t>
+          <t>L15: stray/suspicious non-ASCII glyph(s): U+6D77 CJK UNIFIED IDEOGRAPH-6D77 | isolated marker/symbol line :: 海</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -735,19 +735,15 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Service of the Subp Ã¦ na is by delivering a copy to the</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: own showingâ€”(where the defendant is to be served out</t>
-        </is>
-      </c>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+5236 CJK UNIFIED IDEOGRAPH-5236 | isolated marker/symbol line :: 制</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 26</t>
+          <t>L16: stray/suspicious non-ASCII glyph(s): U+91D1 CJK UNIFIED IDEOGRAPH-91D1 | isolated marker/symbol line :: 金</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -774,12 +770,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -788,17 +784,17 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of the jurisdiction, add the following words)â€”without</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>L42: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: at Osgoode Hall in the City of Toronto ； and you do</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L71: symbol-only separator/garbage line :: 238;</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+5236 CJK UNIFIED IDEOGRAPH-5236 | isolated marker/symbol line :: 制</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -839,17 +835,17 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: memorandum, with these words.â€”" A Defendant is to answer or demur,</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>L96: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L74: symbol-only separator/garbage line :: 391;</t>
+          <t>L34: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -896,7 +892,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 200</t>
+          <t>L71: symbol-only separator/garbage line :: 238;</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -943,7 +939,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: ,</t>
+          <t>L74: symbol-only separator/garbage line :: 391;</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -990,7 +986,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: 4</t>
+          <t>L79: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -1013,12 +1009,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1033,7 +1029,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: X</t>
+          <t>L85: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1061,7 +1057,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1076,7 +1072,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: T</t>
+          <t>L86: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1099,7 +1095,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1117,7 +1113,11 @@
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>L96: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
+        </is>
+      </c>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
@@ -1156,7 +1156,11 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L105: isolated marker/symbol line :: X</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
@@ -1195,7 +1199,11 @@
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="1" t="inlineStr"/>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>L108: isolated marker/symbol line :: T</t>
+        </is>
+      </c>
       <c r="O14" s="1" t="inlineStr"/>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
